--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484699_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484699_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9803</v>
+        <v>5.9555</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4194</v>
+        <v>2.568</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5609</v>
+        <v>3.3875</v>
       </c>
       <c r="G2" t="n">
         <v>4.0356</v>
@@ -610,13 +610,13 @@
         <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6777</v>
+        <v>2.6529</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5257</v>
+        <v>1.6742</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1521</v>
+        <v>0.9787</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6493</v>
+        <v>5.3226</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9041</v>
+        <v>2.6269</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7452</v>
+        <v>2.6957</v>
       </c>
       <c r="G3" t="n">
         <v>0.2668</v>
@@ -688,13 +688,13 @@
         <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>4.016</v>
+        <v>2.6893</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1116</v>
+        <v>1.8345</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9043</v>
+        <v>0.8548</v>
       </c>
       <c r="V3" t="n">
         <v>1.267</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3923</v>
+        <v>5.2622</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4034</v>
+        <v>1.8431</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9889</v>
+        <v>3.4191</v>
       </c>
       <c r="G4" t="n">
         <v>2.9005</v>
@@ -766,13 +766,13 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7038</v>
+        <v>0.5737</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7157</v>
+        <v>-0.276</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4195</v>
+        <v>0.8497</v>
       </c>
       <c r="V4" t="n">
         <v>0.3219</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MORTE MONTAÑES</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9256</v>
+        <v>2.9815</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9256</v>
+        <v>0.3859</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.5956</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9256</v>
+        <v>2.9398</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3005</v>
+        <v>2.2699</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6251</v>
+        <v>0.67</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9256</v>
+        <v>1.5329</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3005</v>
+        <v>2.0807</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6251</v>
+        <v>-0.5478</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.4069</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.1891</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.2178</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.1412</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.6855</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.4557</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>P. MORTE MONTAÑES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7687</v>
+        <v>1.9256</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3562</v>
+        <v>1.9256</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1249</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9398</v>
+        <v>1.9256</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2699</v>
+        <v>1.3005</v>
       </c>
       <c r="I6" t="n">
-        <v>0.67</v>
+        <v>0.6251</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5329</v>
+        <v>1.9256</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0807</v>
+        <v>1.3005</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5478</v>
+        <v>0.6251</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4069</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1891</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2178</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0716</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0565</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5508</v>
+        <v>1.0762</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3333</v>
+        <v>-0.0309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8841</v>
+        <v>1.1071</v>
       </c>
       <c r="G7" t="n">
         <v>1.0724</v>
@@ -1000,13 +1000,13 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6394</v>
+        <v>-0.1141</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6606</v>
+        <v>-0.3582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0212</v>
+        <v>0.2441</v>
       </c>
       <c r="V7" t="n">
         <v>0.3011</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. NOS BARBERA</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5073</v>
+        <v>0.6429</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1652</v>
+        <v>1.0615</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6725</v>
+        <v>-0.4186</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5128</v>
+        <v>1.6133</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2564</v>
+        <v>0.8629</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2564</v>
+        <v>0.7504</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.9068</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.0279</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.8789</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5128</v>
+        <v>-0.2935</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2564</v>
+        <v>-0.165</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2564</v>
+        <v>-0.1285</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1833</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1888</v>
+        <v>1.4798</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1652</v>
+        <v>0.9872</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0236</v>
+        <v>0.4926</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>M. NOS BARBERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.228</v>
+        <v>0.6367</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6218</v>
+        <v>-0.1101</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3938</v>
+        <v>0.7468</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6133</v>
+        <v>0.5128</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8629</v>
+        <v>0.2564</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7504</v>
+        <v>0.2564</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9068</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0279</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8789</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2935</v>
+        <v>0.5128</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.165</v>
+        <v>0.2564</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1285</v>
+        <v>0.2564</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0649</v>
+        <v>-0.0594</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5475</v>
+        <v>-0.1101</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5174</v>
+        <v>0.0507</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1299</v>
+        <v>-0.2749</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1804</v>
+        <v>0.4516</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9495</v>
+        <v>-0.7265</v>
       </c>
       <c r="G10" t="n">
         <v>2.7297</v>
@@ -1234,13 +1234,13 @@
         <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6213</v>
+        <v>0.2336</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5324</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5889</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6381</v>
+        <v>-2.7256</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1303</v>
+        <v>-3.2921</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4922</v>
+        <v>0.5665</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4447</v>
@@ -1312,13 +1312,13 @@
         <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.188</v>
+        <v>0.7245</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3492</v>
+        <v>0.4891</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1611</v>
+        <v>0.2355</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6231</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7846</v>
+        <v>-4.2518</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0989</v>
+        <v>-5.3183</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3143</v>
+        <v>1.0666</v>
       </c>
       <c r="G12" t="n">
         <v>0.0477</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8695</v>
+        <v>1.4023</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0423</v>
+        <v>0.8228</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8273</v>
+        <v>0.5795</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1362</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.4497</v>
+        <v>16.5509</v>
       </c>
       <c r="E13" t="n">
-        <v>1.009999999999998</v>
+        <v>2.111200000000003</v>
       </c>
       <c r="F13" t="n">
-        <v>14.4397</v>
+        <v>14.4398</v>
       </c>
       <c r="G13" t="n">
         <v>17.5995</v>
@@ -1438,7 +1438,7 @@
         <v>7.982800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>9.616900000000001</v>
+        <v>9.616899999999999</v>
       </c>
       <c r="J13" t="n">
         <v>12.4209</v>
@@ -1456,7 +1456,7 @@
         <v>1.4946</v>
       </c>
       <c r="O13" t="n">
-        <v>3.684000000000001</v>
+        <v>3.684</v>
       </c>
       <c r="P13" t="n">
         <v>-6.4139</v>
@@ -1465,16 +1465,16 @@
         <v>-15.577</v>
       </c>
       <c r="R13" t="n">
-        <v>9.162700000000001</v>
+        <v>9.162699999999997</v>
       </c>
       <c r="S13" t="n">
-        <v>9.6228</v>
+        <v>10.7238</v>
       </c>
       <c r="T13" t="n">
-        <v>4.7475</v>
+        <v>5.848599999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>4.8754</v>
+        <v>4.8753</v>
       </c>
       <c r="V13" t="n">
         <v>-5.358700000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0602</v>
+        <v>3.3792</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0842</v>
+        <v>1.4164</v>
       </c>
       <c r="F14" t="n">
-        <v>0.976</v>
+        <v>1.9628</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.3532</v>
+        <v>3.103</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.728</v>
+        <v>2.8915</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3748</v>
+        <v>0.2116</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3919</v>
+        <v>1.879</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2411</v>
+        <v>2.4367</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1508</v>
+        <v>-0.5577</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7451</v>
+        <v>1.224</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9691</v>
+        <v>0.4548</v>
       </c>
       <c r="O14" t="n">
-        <v>0.224</v>
+        <v>0.7692</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1991</v>
+        <v>0.9163</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3823</v>
+        <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6462</v>
+        <v>-1.2736</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6086</v>
+        <v>-0.1798</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0376</v>
+        <v>-1.0937</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5681</v>
+        <v>0.6335</v>
       </c>
       <c r="W14" t="n">
-        <v>1.267</v>
+        <v>0.6335</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7746</v>
+        <v>2.3629</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9356</v>
+        <v>1.3534</v>
       </c>
       <c r="F15" t="n">
-        <v>1.839</v>
+        <v>1.0094</v>
       </c>
       <c r="G15" t="n">
-        <v>3.103</v>
+        <v>-1.3532</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8915</v>
+        <v>-1.728</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2116</v>
+        <v>0.3748</v>
       </c>
       <c r="J15" t="n">
-        <v>1.879</v>
+        <v>0.3919</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4367</v>
+        <v>0.2411</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5577</v>
+        <v>0.1508</v>
       </c>
       <c r="M15" t="n">
-        <v>1.224</v>
+        <v>-1.7451</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4548</v>
+        <v>-1.9691</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7692</v>
+        <v>0.224</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8326</v>
+        <v>2.3823</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8782</v>
+        <v>-0.0511</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6606</v>
+        <v>-0.1221</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2176</v>
+        <v>0.0711</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6335</v>
+        <v>1.5681</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>M. POVEDA CASTELLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4453</v>
+        <v>-0.7486</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6511</v>
+        <v>-1.8714</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2058</v>
+        <v>1.1228</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1826</v>
+        <v>-2.3776</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7531</v>
+        <v>-2.2621</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4295</v>
+        <v>-0.1155</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5684</v>
+        <v>-0.3361</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5169</v>
+        <v>-1.6636</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0515</v>
+        <v>1.3275</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.751</v>
+        <v>-2.0415</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.27</v>
+        <v>-0.5985</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.481</v>
+        <v>-1.443</v>
       </c>
       <c r="P16" t="n">
+        <v>2.3823</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.1833</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.8326</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.6493</v>
+        <v>2.5656</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5986</v>
+        <v>-2.0204</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2911</v>
+        <v>-1.3729</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3074</v>
+        <v>-0.6475</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3219</v>
+        <v>0.0208</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.2461</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2128</v>
+        <v>-0.8005</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.891</v>
+        <v>-1.6026</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6782</v>
+        <v>0.8021</v>
       </c>
       <c r="G17" t="n">
         <v>0.2257</v>
@@ -1780,13 +1780,13 @@
         <v>0.5498</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.072</v>
+        <v>-0.6597</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4404</v>
+        <v>-0.152</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.5077</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. POVEDA CASTELLO</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2381</v>
+        <v>-1.0995</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3522</v>
+        <v>-1.1318</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1141</v>
+        <v>0.0324</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3776</v>
+        <v>-1.1826</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2621</v>
+        <v>-0.7531</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1155</v>
+        <v>-0.4295</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3361</v>
+        <v>0.5684</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6636</v>
+        <v>0.5169</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3275</v>
+        <v>0.0515</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0415</v>
+        <v>-1.751</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5985</v>
+        <v>-1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.443</v>
+        <v>-0.481</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3823</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5656</v>
+        <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.5098</v>
+        <v>-0.0556</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.8537</v>
+        <v>-0.1896</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6561</v>
+        <v>0.134</v>
       </c>
       <c r="V18" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0208</v>
+        <v>0.3219</v>
       </c>
       <c r="X18" t="n">
-        <v>1.2461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5116</v>
+        <v>-1.9705</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9029</v>
+        <v>-2.2875</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3913</v>
+        <v>0.317</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8467</v>
@@ -1936,13 +1936,13 @@
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7016</v>
+        <v>0.2426</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2738</v>
+        <v>-0.1108</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4278</v>
+        <v>0.3535</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2728</v>
+        <v>-2.6986</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3504</v>
+        <v>-2.4778</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9223</v>
+        <v>-0.2208</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6201</v>
+        <v>-2.6423</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4916</v>
+        <v>0.0503</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1286</v>
+        <v>-2.6926</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7652</v>
+        <v>-1.8206</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4335</v>
+        <v>-0.09</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1987</v>
+        <v>-1.7306</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8549</v>
+        <v>-0.8217</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.925</v>
+        <v>0.1403</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.962</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1833</v>
+        <v>2.0158</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0925</v>
+        <v>-1.7502</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7526</v>
+        <v>-0.6572</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3398</v>
+        <v>-1.093</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
       <c r="W20" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7578</v>
+        <v>-2.7075</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9586</v>
+        <v>-1.062</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7993</v>
+        <v>-1.6455</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6423</v>
+        <v>-2.6201</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0503</v>
+        <v>-0.4916</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6926</v>
+        <v>-2.1286</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8206</v>
+        <v>-0.7652</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.09</v>
+        <v>0.4335</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7306</v>
+        <v>-1.1987</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8217</v>
+        <v>-1.8549</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1403</v>
+        <v>-0.925</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.962</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>2.0158</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.8094</v>
+        <v>-0.5271</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.138</v>
+        <v>-0.4642</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.6714</v>
+        <v>-0.063</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7824</v>
+        <v>-4.4823</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7703</v>
+        <v>-3.578</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0121</v>
+        <v>-0.9043</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8145</v>
@@ -2170,13 +2170,13 @@
         <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7846</v>
+        <v>-1.4845</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8454</v>
+        <v>-0.6531</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9392</v>
+        <v>-0.8315</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0639</v>
+        <v>-5.4024</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5832</v>
+        <v>-3.1985</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4807</v>
+        <v>-2.2039</v>
       </c>
       <c r="G23" t="n">
         <v>-6.0913</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4228</v>
+        <v>-0.7613</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3582</v>
+        <v>-0.9736</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0646</v>
+        <v>0.2123</v>
       </c>
       <c r="V23" t="n">
         <v>1.267</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.4499</v>
+        <v>-14.1678</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.4399</v>
+        <v>-14.4398</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.01</v>
+        <v>0.2720000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>-17.5996</v>
@@ -2299,7 +2299,7 @@
         <v>-9.616900000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.178799999999999</v>
+        <v>-5.1788</v>
       </c>
       <c r="K24" t="n">
         <v>-1.4947</v>
@@ -2326,13 +2326,13 @@
         <v>15.5769</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.622900000000001</v>
+        <v>-8.3409</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.8754</v>
+        <v>-4.8753</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.7475</v>
+        <v>-3.4655</v>
       </c>
       <c r="V24" t="n">
         <v>5.358699999999999</v>
